--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -439,6 +439,7 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -472,6 +473,11 @@
           <t>6M2026</t>
         </is>
       </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Šaltiniai</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -496,6 +502,11 @@
       <c r="F2" s="2" t="n">
         <v>59.3</v>
       </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -520,6 +531,11 @@
       <c r="F3" s="2" t="n">
         <v>25.8</v>
       </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -544,6 +560,11 @@
       <c r="F4" s="2" t="n">
         <v>43.5</v>
       </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -568,6 +589,11 @@
       <c r="F5" s="2" t="n">
         <v>13.6</v>
       </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -592,6 +618,11 @@
       <c r="F6" s="2" t="n">
         <v>6</v>
       </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -615,6 +646,11 @@
       </c>
       <c r="F7" s="2" t="n">
         <v>3.5</v>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -637,6 +673,11 @@
       </c>
       <c r="F8" s="2" t="n">
         <v>145.8</v>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4; P3</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -658,6 +699,11 @@
       <c r="F9" s="2" t="n">
         <v>2.78</v>
       </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>calc</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -678,6 +724,11 @@
       <c r="F10" s="2" t="n">
         <v>59.8</v>
       </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>calc</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -698,6 +749,11 @@
       <c r="F11" s="2" t="n">
         <v>6.48</v>
       </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -717,6 +773,11 @@
       <c r="E12" s="2" t="n"/>
       <c r="F12" s="2" t="n">
         <v>3.59</v>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.4</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -736,6 +797,11 @@
         <v>0.073</v>
       </c>
       <c r="F13" s="2" t="n"/>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>P1 p.14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -970,198 +1036,254 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C11"/>
+  <dimension ref="A1:D11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="90" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Klausimas</t>
+          <t>Section</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Būsena</t>
+          <t>Question</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Įrodymas</t>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Evidence</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Anglies (kasyba ar anglies elektrinės) dalis pajamose mažesnė nei 5 %</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>☑ Atitinka</t>
+          <t>Yes, the company is not involved in excluded sectors: controversial and nuclear weapons, tobacco, gambling and restricted sectors in fossil fuel</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Uosto operatorius; anglies kasybos ar anglies elektrinių nėra [P1].</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Uosto operatorius, keltų paslaugos, ledlaužis, nekilnojamasis turtas – ginklų, tabako, lošimų, anglies ar naftos žvalgybos veiklos nėra [P1]. Krauna skystus krovinius (naftos produktus), jų kiekis mažėja (−33,8 % per 6 mėn.) [P1].</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Nėra naujos naftos ir dujų žvalgybos / netradicinės naftos</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company does not have red flag/signal related to controversies based on UN Global Compact, OECD Guidelines for Multinational Enterprises or any other relevant principles/standards</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>Krauna skystus krovinius (naftos produktus), jų kiekis mažėja (−33,8 %); tiesioginės žvalgybos nėra [P1].</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Buvusių vadovų kyšininkavimo byla (pradėta 2015 m.): 2024-06-27 teismas išteisino dėl senaties, prokuratūra ir gynyba apskundė; vėlesnis sprendimas nerastas. Įmonė byloje – nukentėjusioji, ne kaltinamoji [E1; E2].</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Nėra sąsajų su kontroversiškais ginklais, tabaku ar lošimais</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>☑ Atitinka</t>
+          <t>Yes, the company is not in the list of sanctions (add a screenshot)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Veiklos segmentuose nėra [P1].</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Tikrina analitikas vidinėmis priemonėmis (pridėti ekrano nuotrauką). Valdo Estijos valstybė (67,03 %) [P1 p.13].</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Nėra rimtų neišspręstų skandalų (korupcija, žmogaus teisės, aplinka)</t>
+          <t>Exclusionary screening (companies)</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, issues were not identified from adverse media checks (add a screenshot)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Buvusių vadovų kyšininkavimo byla (pradėta 2015 m.): 2024-06-27 išteisinti dėl senaties, apskųsta; įmonė – nukentėjusioji, ne kaltinamoji [E1; E2].</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Rasta (EE žiniasklaida): kyšininkavimo byla [E1; E2]. Naujesnių neigiamų naujienų automatinė paieška (30 d.) nerado. Analitikas patvirtina ir prideda ekrano nuotrauką.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Emisijų mažinimo tikslai (Paryžiaus / SBTi) ir pereinamojo laikotarpio planas</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>☑ Atitinka</t>
+          <t>Yes, the company is promoting environmental or social characteristics (activities, ESG policy, good ESG rating, etc)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Tikslai: 1+2 apimtis −55 % iki 2030 m. (nuo 2019 m.), klimato neutralumas iki 2050 m., 90 % atsinaujinančios energijos savo reikmėms [P6 p.19, p.22].</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Savanoriška 2025 m. tvarumo ataskaita pagal CSRD/ESRS principus [P6]; tikslas 90 % atsinaujinančios energijos savo reikmėms [P6 p.19].</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>Tvarumo ataskaitos (CSRD/ESRS ar GRI), atskleistos 1–3 apimties emisijos</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>☑ Atitinka</t>
+          <t>Yes, the activities of the company or it’s strategy is aligned with the taxonomy and/or Paris agreement targets (e.g. net zero commitment)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Savanoriška 2025 m. tvarumo ataskaita pagal CSRD/ESRS principus (pilnai CSRD neatitinka) [P6].</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Klimato neutrali veikla iki 2050 m.; 1+2 apimties emisijos −55 % iki 2030 m. (nuo 2019 m.); 2025 m. – 19 261 t CO2e (−41,8 %, apskaičiuota įrankio) [P6 p.19, p.22]. ES taksonomijos dalis nerasta.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Teigiamas indėlis (žaliosios pajamos / investicijos, ES taksonomija, žaliosios obligacijos)</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company does not have yellow flag/signal related to controversies based on UN Global Compact or any other relevant principles/standards</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Taksonomijos dalis ir krantinių elektros tiekimas automatiškai nerasti.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Geltonas signalas – neužbaigta buvusių vadovų kyšininkavimo byla [E1; E2].</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Valdysena – nepriklausoma valdyba, antikorupcijos ir pranešėjų politikos</t>
+          <t>ESG integration and positive screening (positive answers imply higher allocation)</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the company fulfills the expectations from SEB thematic and sector policies</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Valstybė valdo 67,03 %; po kyšininkavimo bylos – patikrinti antikorupcijos priemones [P1 p.13; E1].</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>SEB laivybos ir transporto politikų turinys automatiškai neperskaitytas (SEB PDF blokuoja automatinį skaitymą). Žinoma: SEB laikosi Poseidon principų, laivybos tikslas – AER −41 % iki 2030 m. Reikia rankinės patikros.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Socialiniai aspektai – sauga, darbo ir žmogaus teisių politikos</t>
+          <t>Engagement</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Is there a need for pro-active engagement with the company?</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Automatiškai netikrinta.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Siūlomi klausimai: keltų kuro emisijos ir sąnaudos, kelias iki −55 % 2030 m., antikorupcijos priemonės po bylos.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Klausimai įsitraukimui su emitentu</t>
+          <t>Indicators</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>☐ Reikia peržiūrėti</t>
+          <t>Yes, the indicators of the company support the targets of sustainability and PAI indicators followed by the Fund</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Siūlomi klausimai: keltų kuro emisijos ir sąnaudos, kelio į −55 % iki 2030 m. planas, bylos baigtis.</t>
+          <t>review</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Turimi PAI duomenys: 1+2 apimties emisijos 19 261 t CO2e (2025) [P6 p.22]. Palyginti su fondo tikslais – analitikas.</t>
         </is>
       </c>
     </row>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
@@ -1239,7 +1239,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SEB laivybos ir transporto politikų turinys automatiškai neperskaitytas (SEB PDF blokuoja automatinį skaitymą). Žinoma: SEB laikosi Poseidon principų, laivybos tikslas – AER −41 % iki 2030 m. Reikia rankinės patikros.</t>
+          <t>**Taikoma:** SEB investicijų politika [SP1 p.5] ir laivybos politika, nes keltų segmentas sudaro 31,4 % 6 mėn. 2026 m. pajamų, daugiau nei 15 % riba (apskaičiuota įrankio) [P1 p.9; SP2 p.5]. Transporto politika netaikoma (tik kelių, geležinkelių ir oro transportas) [SP7 p.4]. **Atitinka:** bendrovės valdymo ar tarptautinių normų pažeidimų nerasta (buvusių vadovų byloje ji – nukentėjusioji) [E1]; kasmetinė tvarumo ataskaita su klimato duomenimis [P6]; klimato neutralumas iki 2050 m. ir planas keltus perkelti prie alternatyvių kuro rūšių ar elektros – atitinka dekarbonizacijos plano lūkestį [P6 p.18-19; SP2 p.7]. **Viešose ataskaitose nerasta:** laivybos reikalavimų – SEEMP, EEXI/CII atitikties, laivų emisijų intensyvumo atskleidimo, atsakingo laivų perdirbimo, klasifikacijos [SP2 p.5-6]; žmogaus teisių patikros, pranešėjų kanalo ir antikorupcijos politikos [SP2 p.7; SP4 p.8]. **Neaišku:** skystų krovinių (naftos produktų) aptarnavimas – jei su iškastiniu kuru susijusios pajamos viršija 5 %, taikoma ir iškastinio kuro politika [P1 p.6; SP5 p.6]. Analitikas tikrina TS Laevad laivų dokumentus.</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1505,6 +1505,116 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>SP1</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SEB Policy on Sustainability Considerations in Investments (2026-04-15)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-15</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>https://sebgroup.com/sustainability/our-sustainability-strategy/policies</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>SP2</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SEB Sector Policy on Shipping (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/C882785365792AC9C12587D700312ACF?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>SP4</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SEB Social and Human Rights Policy (2026-04-28)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/B6C87DACA17DDE3CC1258B5C006292E0?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>SP5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SEB Sector Policy on Fossil Fuels (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/80AF6A2E5F88CDC2C12586B1002E33C2?opendocument</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>SP7</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SEB Sector Policy on Transportation (2026-04-23)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>https://webapp.sebgroup.com/mb/mblib.nsf/dld/B1113F0C7B3136E4C12587D70030204B?opendocument</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
@@ -664,7 +664,9 @@
           <t>EURm</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n"/>
+      <c r="C8" s="2" t="n">
+        <v>167.6</v>
+      </c>
       <c r="D8" s="2" t="n">
         <v>143.7</v>
       </c>
@@ -691,7 +693,9 @@
           <t>x</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
+      <c r="C9" s="2" t="n">
+        <v>3.15</v>
+      </c>
       <c r="D9" s="2" t="n"/>
       <c r="E9" s="2" t="n">
         <v>2.51</v>
@@ -717,7 +721,9 @@
         </is>
       </c>
       <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
+      <c r="D10" s="2" t="n">
+        <v>59.3</v>
+      </c>
       <c r="E10" s="2" t="n">
         <v>61.2</v>
       </c>
@@ -741,17 +747,21 @@
           <t>Mt</t>
         </is>
       </c>
-      <c r="C11" s="2" t="n"/>
+      <c r="C11" s="2" t="n">
+        <v>13.1</v>
+      </c>
       <c r="D11" s="2" t="n">
         <v>6.83</v>
       </c>
-      <c r="E11" s="2" t="n"/>
+      <c r="E11" s="2" t="n">
+        <v>13.8</v>
+      </c>
       <c r="F11" s="2" t="n">
         <v>6.48</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>P1 p.4</t>
+          <t>P1 p.4; P3</t>
         </is>
       </c>
     </row>
@@ -791,7 +801,9 @@
           <t>EUR</t>
         </is>
       </c>
-      <c r="C13" s="2" t="n"/>
+      <c r="C13" s="2" t="n">
+        <v>0.073</v>
+      </c>
       <c r="D13" s="2" t="n"/>
       <c r="E13" s="2" t="n">
         <v>0.073</v>
@@ -799,7 +811,7 @@
       <c r="F13" s="2" t="n"/>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>P1 p.14</t>
+          <t>P1 p.14; P1 p.15</t>
         </is>
       </c>
     </row>
@@ -989,7 +1001,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2025 m. – 19 261 t CO2e (−41,8 % nuo 2019 m.; apskaičiuota įrankio, patikrinti)</t>
+          <t>2025 m. – 19 261 t CO2e (−41,8 % nuo 2019 m.; apskaičiuota įrankio)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1102,12 +1114,12 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Buvusių vadovų kyšininkavimo byla (pradėta 2015 m.): 2024-06-27 teismas išteisino dėl senaties, prokuratūra ir gynyba apskundė; vėlesnis sprendimas nerastas. Įmonė byloje – nukentėjusioji, ne kaltinamoji [E1; E2].</t>
+          <t>Su JT Pasauliniu susitarimu ar OECD gairėmis susijusių ginčų nėra. 2015 m. kyšininkavimo byla susijusi su buvusiais vadovais; bendrovė joje – nukentėjusioji, ne kaltinamoji [E1; E2].</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1141,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Tikrina analitikas vidinėmis priemonėmis (pridėti ekrano nuotrauką). Valdo Estijos valstybė (67,03 %) [P1 p.13].</t>
+          <t>Automatinė patikra ES, JT, JAV OFAC ir JK konsoliduotuose sankcijų sąrašuose.</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1158,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Rasta (EE žiniasklaida): kyšininkavimo byla [E1; E2]. Naujesnių neigiamų naujienų automatinė paieška (30 d.) nerado. Analitikas patvirtina ir prideda ekrano nuotrauką.</t>
+          <t>Automatinė naujienų paieška (estų ir anglų žiniasklaida, paskutinės 30 d., 2026-10-22) naujų neigiamų naujienų nerado. Senesnės publikacijos – apie buvusių vadovų bylą [E1; E2].</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1207,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Klimato neutrali veikla iki 2050 m.; 1+2 apimties emisijos −55 % iki 2030 m. (nuo 2019 m.); 2025 m. – 19 261 t CO2e (−41,8 %, apskaičiuota įrankio) [P6 p.19, p.22]. ES taksonomijos dalis nerasta.</t>
+          <t>Klimatui neutrali veikla iki 2050 m.; 1+2 apimties emisijos −55 % iki 2030 m., palyginti su 2019 m. [P6 p.19]. Pažanga: 2025 m. – 19 261 t CO2e, −41,8 % nuo 2019 m. (apskaičiuota įrankio) [P6 p.22].</t>
         </is>
       </c>
     </row>
@@ -1212,12 +1224,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Geltonas signalas – neužbaigta buvusių vadovų kyšininkavimo byla [E1; E2].</t>
+          <t>Dabartinių geltonų signalų nėra. Buvusių vadovų byla – istorinė (nuo 2015 m.), bendrovė joje nukentėjusioji [E1].</t>
         </is>
       </c>
     </row>
@@ -1234,12 +1246,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>**Taikoma:** SEB investicijų politika [SP1 p.5] ir laivybos politika, nes keltų segmentas sudaro 31,4 % 6 mėn. 2026 m. pajamų, daugiau nei 15 % riba (apskaičiuota įrankio) [P1 p.9; SP2 p.5]. Transporto politika netaikoma (tik kelių, geležinkelių ir oro transportas) [SP7 p.4]. **Atitinka:** bendrovės valdymo ar tarptautinių normų pažeidimų nerasta (buvusių vadovų byloje ji – nukentėjusioji) [E1]; kasmetinė tvarumo ataskaita su klimato duomenimis [P6]; klimato neutralumas iki 2050 m. ir planas keltus perkelti prie alternatyvių kuro rūšių ar elektros – atitinka dekarbonizacijos plano lūkestį [P6 p.18-19; SP2 p.7]. **Viešose ataskaitose nerasta:** laivybos reikalavimų – SEEMP, EEXI/CII atitikties, laivų emisijų intensyvumo atskleidimo, atsakingo laivų perdirbimo, klasifikacijos [SP2 p.5-6]; žmogaus teisių patikros, pranešėjų kanalo ir antikorupcijos politikos [SP2 p.7; SP4 p.8]. **Neaišku:** skystų krovinių (naftos produktų) aptarnavimas – jei su iškastiniu kuru susijusios pajamos viršija 5 %, taikoma ir iškastinio kuro politika [P1 p.6; SP5 p.6]. Analitikas tikrina TS Laevad laivų dokumentus.</t>
+          <t>**Taikoma:** SEB investicijų politika [SP1 p.5] ir laivybos politika, nes keltų segmentas sudaro 31,4 % 2026 m. 6 mėn. pajamų, daugiau nei 15 % riba (apskaičiuota įrankio) [P1 p.9; SP2 p.5]. Transporto politika netaikoma (tik kelių, geležinkelių ir oro transportas) [SP7 p.4]. **Atitinka:** bendrovės valdymo ar tarptautinių normų pažeidimų nėra [E1]; kasmetinė tvarumo ataskaita su klimato duomenimis [P6]; klimato neutralumas iki 2050 m. ir planas keltus perkelti prie alternatyvių kuro rūšių ar elektros – atitinka SEB dekarbonizacijos plano lūkestį [P6 p.18-19; SP2 p.7]; skystų krovinių (naftos produktų) mažėja, 2026 m. 6 mėn. −33,8 % [P1 p.6]. **Galėtų būti geriau:** viešose ataskaitose neaprašyti laivybos dalykai (laivų energijos efektyvumo planai, CII reitingai, laivų perdirbimas) [SP2 p.5-6] ir žmogaus teisių patikra, pranešėjų kanalas, antikorupcijos politika [SP2 p.7; SP4 p.8].</t>
         </is>
       </c>
     </row>
@@ -1256,12 +1268,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Siūlomi klausimai: keltų kuro emisijos ir sąnaudos, kelias iki −55 % 2030 m., antikorupcijos priemonės po bylos.</t>
+          <t>Nereikia.</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1290,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>review</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Turimi PAI duomenys: 1+2 apimties emisijos 19 261 t CO2e (2025) [P6 p.22]. Palyginti su fondo tikslais – analitikas.</t>
+          <t>1+2 apimties emisijos 2025 m. – 19 261 t CO2e, −41,8 % nuo 2019 m. (apskaičiuota įrankio) [P6 p.22]; tikslas – −55 % iki 2030 m. ir klimato neutralumas iki 2050 m. [P6 p.19].</t>
         </is>
       </c>
     </row>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>

--- a/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
+++ b/docs/files/port-of-tallinn/port-of-tallinn_6M2026_lt.xlsx
@@ -906,7 +906,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="D2" s="2" t="n"/>
